--- a/data/Tecmo Statistics Current.xlsx
+++ b/data/Tecmo Statistics Current.xlsx
@@ -1909,7 +1909,7 @@
     <t>AFC Divisional Playoff Loss to PIT (WB) 13 - 10 OT</t>
   </si>
   <si>
-    <t>SF (COMP) Elimanted PHI (AD) 24-21 in the NFCCG.</t>
+    <t>SF (COMP) Eliminated PHI (AD) 24-21 in the NFCCG.</t>
   </si>
   <si>
     <t>Caught 44 receptions for over 2,000 yards and 30 TDs from the absymal Mark Rypien, leading the Skins to the NFC Championship game.</t>
